--- a/Documents/十五音教材/聲調對照表.xlsx
+++ b/Documents/十五音教材/聲調對照表.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\Documents\十五音教材\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\Documents\十五音教材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0175019-E9B7-4523-BEB9-83A48DBD9BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F70A5F-B683-4DE6-86CE-D0D451B03B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{08BCE876-220B-4617-985F-BC533BEFAD68}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{08BCE876-220B-4617-985F-BC533BEFAD68}"/>
   </bookViews>
   <sheets>
-    <sheet name="聲調對照表" sheetId="1" r:id="rId1"/>
-    <sheet name="聲調對照表 (3)" sheetId="3" r:id="rId2"/>
-    <sheet name="聲調對照表 (2)" sheetId="2" r:id="rId3"/>
+    <sheet name="W音調對照表" sheetId="4" r:id="rId1"/>
+    <sheet name="W音調對照表 (2)" sheetId="5" r:id="rId2"/>
+    <sheet name="聲調對照表" sheetId="1" r:id="rId3"/>
+    <sheet name="聲調對照表 (3)" sheetId="3" r:id="rId4"/>
+    <sheet name="聲調對照表 (2)" sheetId="2" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="十五音韻母">'[1]十五音-韻母'!$C$5:$C$54</definedName>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="62">
   <si>
     <t>˙</t>
   </si>
@@ -221,12 +223,80 @@
     <t>]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>君</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>閩拼調號</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>音調名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kut4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -392,6 +462,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -419,7 +503,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -468,6 +552,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -482,7 +601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -588,6 +707,78 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -596,7 +787,437 @@
     <cellStyle name="一般 4 2" xfId="1" xr:uid="{EA1B35F1-F8C7-4DBF-80A8-32E3C86E8708}"/>
     <cellStyle name="一般 5" xfId="4" xr:uid="{1764E436-0C56-4749-A903-F277CDD5CEB5}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <name val="Noto Sans TC"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="28"/>
+        <color theme="1"/>
+        <name val="Noto Sans TC"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="28"/>
+        <color theme="1"/>
+        <name val="Noto Sans TC"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="36"/>
+        <color theme="1"/>
+        <name val="Noto Sans TC Medium"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="28"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="22"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Noto Serif TC Black"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Noto Serif TC Black"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Noto Serif TC Black"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="36"/>
+        <color theme="1"/>
+        <name val="Noto Serif TC Black"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -12673,6 +13294,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="env"/>
@@ -12710,6 +13332,23 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF148CB2-F379-40E3-98F3-F78C8AAD8794}" name="表格1" displayName="表格1" ref="B2:J9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="13" totalsRowBorderDxfId="12" headerRowCellStyle="一般 3">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{CC4F6348-3AF4-4581-8648-C3F3C3A3481E}" name="漢字" dataDxfId="11" dataCellStyle="一般 5"/>
+    <tableColumn id="2" xr3:uid="{B6FE4FE8-7A8D-4FC0-A1E4-0C2AA7513AB6}" name="台語音標" dataDxfId="10" dataCellStyle="一般 5"/>
+    <tableColumn id="3" xr3:uid="{AB1E00D9-E9FA-4679-A432-D0A2CB859219}" name="四聲八調" dataDxfId="9" dataCellStyle="一般 5"/>
+    <tableColumn id="4" xr3:uid="{5769BADB-0B09-4B0A-97A6-1689F7E8257A}" name="音調名" dataDxfId="8" dataCellStyle="一般 5"/>
+    <tableColumn id="5" xr3:uid="{22D7CCC0-8104-498F-9FCE-B1A1056BB231}" name="調值" dataDxfId="7" dataCellStyle="一般 2"/>
+    <tableColumn id="6" xr3:uid="{A759BC52-68FB-45E1-83FC-9E2ACC1F1DDC}" name="鍵盤按鍵" dataDxfId="6" dataCellStyle="一般 2"/>
+    <tableColumn id="7" xr3:uid="{6D3C0B43-6A0E-4EC6-8136-CEDBA842C830}" name="方音符號" dataDxfId="5" dataCellStyle="一般 4 2"/>
+    <tableColumn id="8" xr3:uid="{3185A5F8-8F89-4986-8B88-2EE0FCB1EE6E}" name="台羅調號" dataDxfId="4" dataCellStyle="一般 3"/>
+    <tableColumn id="9" xr3:uid="{707D4466-BB96-4CD5-8B0A-CED935AC0C40}" name="閩拼調號" dataDxfId="3" dataCellStyle="一般 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13028,6 +13667,564 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D5D97F-1E13-4BC8-9B15-F9B539AA4D38}">
+  <dimension ref="B2:J18"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="25.5">
+      <c r="B2" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="59.25">
+      <c r="B3" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="40">
+        <v>44</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="43">
+        <v>1</v>
+      </c>
+      <c r="J3" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="59.25">
+      <c r="B4" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="40">
+        <v>33</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="43">
+        <v>7</v>
+      </c>
+      <c r="J4" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="59.25">
+      <c r="B5" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="40">
+        <v>31</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="43">
+        <v>3</v>
+      </c>
+      <c r="J5" s="44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="59.25">
+      <c r="B6" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="40">
+        <v>51</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="43">
+        <v>2</v>
+      </c>
+      <c r="J6" s="44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="59.25">
+      <c r="B7" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="40">
+        <v>24</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="43">
+        <v>5</v>
+      </c>
+      <c r="J7" s="44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="59.25">
+      <c r="B8" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="40">
+        <v>30</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="43">
+        <v>4</v>
+      </c>
+      <c r="J8" s="44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="59.25">
+      <c r="B9" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="52">
+        <v>50</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="55">
+        <v>8</v>
+      </c>
+      <c r="J9" s="56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="57.75" outlineLevel="1">
+      <c r="B18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <f xml:space="preserve"> "dong" &amp; I18</f>
+        <v>dong6</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10">
+        <v>53</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="10">
+        <v>6</v>
+      </c>
+      <c r="J18" s="9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD041BE-7FEF-4C5B-BC98-BC5ECF479331}">
+  <dimension ref="B2:J18"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="25.5">
+      <c r="B2" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="D2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="59.25">
+      <c r="B3" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="31">
+        <v>44</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="24">
+        <v>1</v>
+      </c>
+      <c r="J3" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="59.25">
+      <c r="B4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="32">
+        <v>33</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="25">
+        <v>7</v>
+      </c>
+      <c r="J4" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="59.25">
+      <c r="B5" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="31">
+        <v>31</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="24">
+        <v>3</v>
+      </c>
+      <c r="J5" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="59.25">
+      <c r="B6" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="32">
+        <v>51</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="25">
+        <v>2</v>
+      </c>
+      <c r="J6" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="59.25">
+      <c r="B7" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="31">
+        <v>24</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="24">
+        <v>5</v>
+      </c>
+      <c r="J7" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="59.25">
+      <c r="B8" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="32">
+        <v>30</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="25">
+        <v>4</v>
+      </c>
+      <c r="J8" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="59.25">
+      <c r="B9" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="31">
+        <v>50</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24">
+        <v>8</v>
+      </c>
+      <c r="J9" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="57.75" outlineLevel="1">
+      <c r="B18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <f xml:space="preserve"> "dong" &amp; I18</f>
+        <v>dong6</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10">
+        <v>53</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="10">
+        <v>6</v>
+      </c>
+      <c r="J18" s="9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8264B7F8-EC6F-425C-A778-2C680D504D26}">
   <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
@@ -13063,7 +14260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="65.25">
+    <row r="3" spans="2:9" ht="50.25">
       <c r="B3" s="18" t="s">
         <v>26</v>
       </c>
@@ -13090,7 +14287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="65.25">
+    <row r="4" spans="2:9" ht="50.25">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -13117,7 +14314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="65.25">
+    <row r="5" spans="2:9" ht="50.25">
       <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
@@ -13144,7 +14341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="65.25">
+    <row r="6" spans="2:9" ht="50.25">
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
@@ -13171,7 +14368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="65.25">
+    <row r="7" spans="2:9" ht="50.25">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -13198,7 +14395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="65.25">
+    <row r="8" spans="2:9" ht="50.25">
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
@@ -13224,7 +14421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="65.25">
+    <row r="9" spans="2:9" ht="50.25">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
@@ -13284,7 +14481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1050C03-4A49-40F3-8140-C9DAF6B05C63}">
   <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
@@ -13320,7 +14517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="65.25">
+    <row r="3" spans="2:9" ht="50.25">
       <c r="B3" s="18" t="s">
         <v>26</v>
       </c>
@@ -13347,7 +14544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="65.25">
+    <row r="4" spans="2:9" ht="50.25">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -13374,7 +14571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="65.25">
+    <row r="5" spans="2:9" ht="50.25">
       <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
@@ -13401,7 +14598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="65.25">
+    <row r="6" spans="2:9" ht="50.25">
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
@@ -13428,7 +14625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="65.25">
+    <row r="7" spans="2:9" ht="50.25">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -13455,7 +14652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="65.25">
+    <row r="8" spans="2:9" ht="50.25">
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
@@ -13481,7 +14678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="65.25">
+    <row r="9" spans="2:9" ht="50.25">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
@@ -13541,7 +14738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1566D659-7E1D-42E7-9495-78EC72F6C0D2}">
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
@@ -13581,7 +14778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="65.25">
+    <row r="3" spans="2:10" ht="59.25">
       <c r="B3" s="18" t="s">
         <v>26</v>
       </c>
@@ -13611,7 +14808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="65.25">
+    <row r="4" spans="2:10" ht="59.25">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -13641,7 +14838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="65.25">
+    <row r="5" spans="2:10" ht="59.25">
       <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
@@ -13671,7 +14868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="65.25">
+    <row r="6" spans="2:10" ht="59.25">
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
@@ -13701,7 +14898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="65.25">
+    <row r="7" spans="2:10" ht="59.25">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -13731,7 +14928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="65.25">
+    <row r="8" spans="2:10" ht="59.25">
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
@@ -13760,7 +14957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="65.25">
+    <row r="9" spans="2:10" ht="59.25">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
